--- a/AAII_Financials/Quarterly/ESAB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ESAB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
   <si>
     <t>ESAB</t>
   </si>
@@ -656,338 +656,351 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E7" s="2">
         <v>46115</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45933</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45842</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45751</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45562</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45471</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45380</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45198</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44743</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44652</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44470</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44379</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44288</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>807600</v>
+      </c>
+      <c r="E8" s="3">
         <v>745600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>721000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>727800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>715600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>678100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>670800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>673300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>707100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>689700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>689300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>681000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>720400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>684000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>664100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>620300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1309100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>647900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>624200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>606000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>629800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>568100</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>500400</v>
+      </c>
+      <c r="E9" s="3">
         <v>470500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>463200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>458500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>449500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>422900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>412400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>419500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>436700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>434700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>434600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>431300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>456500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>436600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>439700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>410900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>857300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>423600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>411400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>399000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>411400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>368300</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>307200</v>
+      </c>
+      <c r="E10" s="3">
         <v>275100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>257800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>269300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>266000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>255200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>258300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>253800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>270300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>255000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>254700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>249700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>263900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>247400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>224400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>209400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>451800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>224300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>212800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>207000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>218400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>199800</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1014,59 +1027,60 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E12" s="3">
         <v>12500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>12900</v>
-      </c>
-      <c r="F12" s="3">
-        <v>10500</v>
       </c>
       <c r="G12" s="3">
         <v>10500</v>
       </c>
       <c r="H12" s="3">
+        <v>10500</v>
+      </c>
+      <c r="I12" s="3">
         <v>10100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>9200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>9700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>10100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>10700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>9000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>9500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>9600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>8900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>8000</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1088,8 +1102,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1162,127 +1179,133 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E14" s="3">
         <v>10200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>39000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>5900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>14100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>5200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>9400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>13100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>8500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>17100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>8900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>8200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>4900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>3600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>3100</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E15" s="3">
         <v>23900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>43300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>21900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>19400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>17500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>36000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>17100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>16500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>16400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>39700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>17500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>17700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>21900</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1310,8 +1333,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1335,156 +1361,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>710600</v>
+      </c>
+      <c r="E17" s="3">
         <v>645000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>599900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>615900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>605100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>563800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>548700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>565400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>582900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>577200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>567900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>576700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>606600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>583900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>585500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>539300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1139600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>564300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>551200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>527300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>547600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>495800</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E18" s="3">
         <v>100600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>121100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>112000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>110500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>114300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>122100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>107900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>124100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>112600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>121500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>104300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>113800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>100100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>78600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>81000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>169500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>83600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>73000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>78700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>82200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>72300</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1511,201 +1544,208 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>7600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1300</v>
       </c>
-      <c r="G20" s="3">
-        <v>-2700</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
         <v>7600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>12400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-12600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-8900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-7400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>11500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>300</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>124900</v>
+      </c>
+      <c r="E21" s="3">
         <v>124500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>156900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>135200</v>
       </c>
-      <c r="G21" s="3">
-        <v>132600</v>
-      </c>
       <c r="H21" s="3">
+        <v>129800</v>
+      </c>
+      <c r="I21" s="3">
         <v>131800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>150500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>124700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>143900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>128500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>148800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>118900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>130300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>123100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>83300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>87800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>195200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>100900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>92600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>98400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>112800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>91200</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E22" s="3">
         <v>25600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>10500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>24900</v>
       </c>
-      <c r="G22" s="3">
-        <v>23700</v>
-      </c>
       <c r="H22" s="3">
+        <v>21000</v>
+      </c>
+      <c r="I22" s="3">
         <v>16800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>16600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>19200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>16600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>25300</v>
-      </c>
-      <c r="N22" s="3">
-        <v>17600</v>
       </c>
       <c r="O22" s="3">
         <v>17600</v>
       </c>
       <c r="P22" s="3">
+        <v>17600</v>
+      </c>
+      <c r="Q22" s="3">
         <v>20700</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -1733,156 +1773,165 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>48100</v>
+      </c>
+      <c r="E23" s="3">
         <v>64900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>64100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>83000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>88100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>93100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>96500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>89100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>103400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>81400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>77500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>80600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>89800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>71200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>66000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>72100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>162100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>84200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>74000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>78900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>93700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>72500</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E24" s="3">
         <v>13100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>12700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>17700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>18300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>20500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>22900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>18100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>17900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>18500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>17900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>19800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>21000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>37000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>17800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>45800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>25700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>33400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>17400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>15600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>14000</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1955,156 +2004,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E26" s="3">
         <v>51800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>51400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>65300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>69800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>72600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>73600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>71000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>85500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>62900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>59600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>60800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>68800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>34100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>60400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>54300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>116300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>58400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>40600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>61400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>78100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>58500</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E27" s="3">
         <v>47400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>37000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>54700</v>
       </c>
-      <c r="G27" s="3">
-        <v>66700</v>
-      </c>
       <c r="H27" s="3">
+        <v>66900</v>
+      </c>
+      <c r="I27" s="3">
         <v>67100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>53400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>67900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>82500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>59600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>49800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>57100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>65100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>31700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>58400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>52900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>113900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>57100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>39400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>60600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>77400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>57700</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2177,67 +2235,70 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E29" s="3">
         <v>-2600</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-12600</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-8800</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-1700</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-2700</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-18600</v>
-      </c>
-      <c r="J29" s="3">
-        <v>-1200</v>
       </c>
       <c r="K29" s="3">
         <v>-1200</v>
       </c>
       <c r="L29" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="M29" s="3">
         <v>-1300</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-8100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-1700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-1600</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-900</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>1800</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-1000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-3900</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-2000</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2245,14 +2306,17 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>3</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2325,8 +2389,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2399,156 +2466,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>-7600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1300</v>
       </c>
-      <c r="G32" s="3">
-        <v>2700</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
         <v>-7600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-12400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>12600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>8900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>7400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-11500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-300</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E33" s="3">
         <v>47600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>37700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>54800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>66900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>67400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>53700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>68200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>82900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>60000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>50200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>57600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>65600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>31900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>60300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>51900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>109900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>55100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>39400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>60600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>77400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>57700</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2621,161 +2697,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E35" s="3">
         <v>47600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>37700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>54800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>66900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>67400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>53700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>68200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>82900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>60000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>50200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>57600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>65600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>31900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>60300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>51900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>109900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>55100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>39400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>60600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>77400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>57700</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E38" s="2">
         <v>46115</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45933</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45842</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45751</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45562</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45471</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45380</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45198</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44743</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44652</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44470</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44379</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44288</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2802,8 +2887,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2830,65 +2916,66 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>217500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1004800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>185900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>218200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>258200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>291300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>249400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>253700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>228500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>76500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>102000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>82800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>74400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>82100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>72000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>60600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>53500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>56600</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2904,8 +2991,11 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2978,65 +3068,68 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>554100</v>
+      </c>
+      <c r="E43" s="3">
         <v>488500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>451300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>460500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>456100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>414800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>370300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>420900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>431200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>430100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>385200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>388500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>412700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>404100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>374300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>360000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>384200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>410200</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3052,65 +3145,68 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>581500</v>
+      </c>
+      <c r="E44" s="3">
         <v>520600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>481800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>503700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>474100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>450700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>403700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>422700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>426500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>405600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>392900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>425700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>447300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>448300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>416800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>446500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>473800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>462500</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3126,65 +3222,68 @@
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>90800</v>
+      </c>
+      <c r="E45" s="3">
         <v>77300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>76900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>87000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>80600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>72200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>69300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>65500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>63500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>70100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>55900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>70000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>68100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>70300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>125500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>120900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>129800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>118700</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3200,65 +3299,68 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1528500</v>
+      </c>
+      <c r="E46" s="3">
         <v>2170200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1261900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1333700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1336300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1286000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1148400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1221500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1212600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1042700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>997700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1029700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1071600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1060700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>988700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>988000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1041400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1048100</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3274,8 +3376,11 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3294,32 +3399,32 @@
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3">
         <v>800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4200</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
         <v>9500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>16800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>16900</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3348,65 +3453,68 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>533200</v>
+      </c>
+      <c r="E48" s="3">
         <v>483500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>495200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>491700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>415400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>393800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>388200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>390900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>376900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>384600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>389900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>368000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>376900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>381100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>376300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>354700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>381200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>388300</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3422,65 +3530,68 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4118300</v>
+      </c>
+      <c r="E49" s="3">
         <v>2586500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2622700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2647200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2332000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2187700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2140000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2167700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2060400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2071200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2087900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2045300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2091000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2082700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2046900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1852000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1926700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2022500</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3496,8 +3607,11 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3570,8 +3684,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3644,65 +3761,68 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>379000</v>
+      </c>
+      <c r="E52" s="3">
         <v>380600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>323900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>396400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>348100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>349400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>311700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>302300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>312200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>328200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>297000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>295200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>305400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>323600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>342200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>345200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>324400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>322500</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3718,8 +3838,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3792,65 +3915,68 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6562600</v>
+      </c>
+      <c r="E54" s="3">
         <v>5624700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4766100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4869400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4432400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4217500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4034000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4084500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3967100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3827500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3828600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3756000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3862800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3849100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3754000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3539900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3673700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3781300</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,8 +3992,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3894,8 +4023,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3922,65 +4052,66 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>407400</v>
+      </c>
+      <c r="E57" s="3">
         <v>398500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>360400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>342200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>369500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>349700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>318500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>320300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>350100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>338400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>306600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>302600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>333200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>355300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>316300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>320200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>360000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>369000</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3996,53 +4127,56 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E58" s="3">
         <v>26100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>24500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>24700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>42600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>38700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>36500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>21400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>22300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>22900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>22800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>20300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>20200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>22800</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -4070,65 +4204,68 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>175700</v>
+      </c>
+      <c r="E59" s="3">
         <v>164500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>145500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>145200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>135600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>137300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>131100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>128300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>129400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>125400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>127800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>130200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>124100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>125400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>285300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>290400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>282100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>283400</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4144,65 +4281,68 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>779000</v>
+      </c>
+      <c r="E60" s="3">
         <v>730000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>664800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>669100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>686500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>672000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>632100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>637100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>651100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>631300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>620100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>610400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>618400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>630400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>601600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>610600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>642100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>652400</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,62 +4358,65 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2507500</v>
+      </c>
+      <c r="E61" s="3">
         <v>2114000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1320700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1442300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1124200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1118800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1126800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1150200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1149800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1066800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1094700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1164000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1237300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1294800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1218600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1132400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1182200</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4292,65 +4435,68 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>691900</v>
+      </c>
+      <c r="E62" s="3">
         <v>545000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>569100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>596000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>509900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>476300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>466900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>419500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>416800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>447000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>466200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>440600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>460500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>465600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>545300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>549400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>568000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>611600</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4366,8 +4512,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4440,8 +4589,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4514,8 +4666,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4588,65 +4743,68 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3978400</v>
+      </c>
+      <c r="E66" s="3">
         <v>3389000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2554600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2707400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2320600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2267200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2225700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2206800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2217700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2145100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2181000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2214900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2316100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2390900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2403800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2330700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2431800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1304500</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4662,8 +4820,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4690,8 +4851,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4764,8 +4926,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4838,13 +5003,16 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>171100</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
@@ -4912,8 +5080,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4986,65 +5157,68 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>865800</v>
+      </c>
+      <c r="E72" s="3">
         <v>842300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>800800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>769200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>720500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>659700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>597200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>548300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>484900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>406900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>350600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>304000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>250000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>188100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>159200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>101500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>52200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3040900</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5060,8 +5234,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5134,8 +5311,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5208,8 +5388,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5282,65 +5465,68 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2367600</v>
+      </c>
+      <c r="E76" s="3">
         <v>2190800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2166000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2115900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2069600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1909700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1769000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1837100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1708000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1640800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1607400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1500800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1506300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1419600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1350200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1209200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1241900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2476900</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5356,8 +5542,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5430,161 +5619,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E80" s="2">
         <v>46115</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45933</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45842</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45751</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45562</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45471</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45380</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45198</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44743</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44652</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44470</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44379</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44288</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E81" s="3">
         <v>47600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>37700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>54800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>66900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>67400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>53700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>68200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>82900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>60000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>50200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>57600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>65600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>31900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>60300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>51900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>109900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>55100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>39400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>60600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>77400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>57700</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5611,82 +5809,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E83" s="3">
         <v>17500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>16600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>17100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>12600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>17500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>17700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>21900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>16400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>15600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>16400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>16700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>17300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>15600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>33100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>16700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>18600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>19500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>19100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>18700</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5759,8 +5961,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5833,8 +6038,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5907,8 +6115,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5981,8 +6192,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6055,82 +6269,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E89" s="3">
         <v>46900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>97100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>81500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>46600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>35400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>126900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>101000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>83000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>44500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>122400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>107400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>62700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>38100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>91400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>79500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>43400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>16100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>58700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>69500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>59800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>62800</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6157,82 +6377,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-19600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-24700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-19300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-18200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-16700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-8000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-6100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6305,8 +6529,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6379,82 +6606,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1487000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-363600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-95800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-91500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-77300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-10300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-26600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-19900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-166700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-10300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-12600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-8300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6481,8 +6714,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6496,7 +6730,7 @@
         <v>6100</v>
       </c>
       <c r="G96" s="3">
-        <v>4900</v>
+        <v>6100</v>
       </c>
       <c r="H96" s="3">
         <v>4900</v>
@@ -6508,7 +6742,7 @@
         <v>4900</v>
       </c>
       <c r="K96" s="3">
-        <v>3600</v>
+        <v>4900</v>
       </c>
       <c r="L96" s="3">
         <v>3600</v>
@@ -6520,17 +6754,17 @@
         <v>3600</v>
       </c>
       <c r="O96" s="3">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="P96" s="3">
         <v>3000</v>
       </c>
       <c r="Q96" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-3000</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -6555,8 +6789,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6629,8 +6866,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6703,8 +6943,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6777,226 +7020,238 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>661800</v>
+      </c>
+      <c r="E100" s="3">
         <v>786200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-113600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>246900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-13100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>80200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-33900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-77500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-74300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-60800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>80200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-52800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-19900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-45900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-63800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-55800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-56100</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E101" s="3">
         <v>22400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-30800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>7100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-15600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>6500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-12200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>6500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-12200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-787300</v>
+      </c>
+      <c r="E102" s="3">
         <v>818900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-32400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-40000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-33100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>42000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>25200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>152000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-25500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>19200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>8400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>10000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>11400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>7200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>12300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>15400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
